--- a/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/CRONOGRAMA_MESTRE_SUPRIMENTOS_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/CRONOGRAMA_MESTRE_SUPRIMENTOS_TMULT.xlsx
@@ -529,35 +529,21 @@
   </sheetPr>
   <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA MESTRE DE SUPRIMENTOS: MATERIAIS &amp; INSUMOS (OBRA_TMULT)</t>
+          <t>CRONOGRAMA MESTRE DE SUPRIMENTOS: MATERIAIS &amp; INSUMOS (TMULT)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edifício Administrativo (368,40 m²) - Porto do Açu | Prazos de Gatilho vs Lead Time POP 05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>TMULT — Terminal Multiuso (Porto do Açu) — Edifício Administrativo | Prazos de Gatilho vs Lead Time POP 05</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1972,28 +1958,14 @@
   </sheetPr>
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HISTOGRAMA E CRONOGRAMA DE MOBILIZAÇÃO DE EQUIPAMENTOS (OBRA_TMULT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>CRONOGRAMA DE EQUIPAMENTOS &amp; LOCAÇÕES (TMULT)</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3002,24 +2974,14 @@
   </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLANO MESTRE DE CONTRATAÇÃO DE EMPREITEIROS (OBRA_TMULT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>PLANO MESTRE DE CONTRATAÇÃO DE EMPREITEIROS (TMULT)</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
